--- a/ForHome8/DataScience/data_audit_task01.xlsx
+++ b/ForHome8/DataScience/data_audit_task01.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t xml:space="preserve">count</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the diagrams it looks like there are three main clusters.</t>
   </si>
 </sst>
 </file>
@@ -185,9 +188,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>337680</xdr:colOff>
+      <xdr:colOff>337320</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>65880</xdr:rowOff>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -201,7 +204,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9720" y="1418760"/>
-          <a:ext cx="4905000" cy="3981240"/>
+          <a:ext cx="4905360" cy="3980880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -222,9 +225,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>239760</xdr:colOff>
+      <xdr:colOff>239400</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>37080</xdr:rowOff>
+      <xdr:rowOff>36720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -237,8 +240,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5294880" y="837720"/>
-          <a:ext cx="4723920" cy="4723920"/>
+          <a:off x="5295600" y="837720"/>
+          <a:ext cx="4727880" cy="4723560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -264,9 +267,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -279,8 +282,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -306,9 +309,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -321,8 +324,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -342,10 +345,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4.48"/>
@@ -475,6 +478,11 @@
       </c>
       <c r="M3" s="0" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -495,7 +503,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B301"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2923,7 +2931,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B301"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
